--- a/فیچر لیست های زیرساخت.xlsx
+++ b/فیچر لیست های زیرساخت.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WaveProject\WFTInfra\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WFTProjects\WFTInfra\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7995"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7995" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="لیست فیچرها" sheetId="2" r:id="rId1"/>
     <sheet name="اولویت بندی " sheetId="3" r:id="rId2"/>
+    <sheet name="فیچر مدیریت کاربران" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'اولویت بندی '!#REF!</definedName>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="95">
   <si>
     <t>ردیف</t>
   </si>
@@ -254,6 +255,66 @@
   </si>
   <si>
     <t>اولویت</t>
+  </si>
+  <si>
+    <t>ثبت‌نام کاربر (User Registration)</t>
+  </si>
+  <si>
+    <t>ورود کاربر (User Login)</t>
+  </si>
+  <si>
+    <t>بازیابی رمز عبور (Forgot/Reset Password)</t>
+  </si>
+  <si>
+    <t>تغییر رمز عبور (Change Password)</t>
+  </si>
+  <si>
+    <t>تأیید ایمیل (Email Confirmation)</t>
+  </si>
+  <si>
+    <t>احراز هویت با Token یا JWT</t>
+  </si>
+  <si>
+    <t>مدیریت نقش‌ها (Role Management)</t>
+  </si>
+  <si>
+    <t>مدیریت مجوزها (Permission Management)</t>
+  </si>
+  <si>
+    <t>لیست کاربران (User Listing)</t>
+  </si>
+  <si>
+    <t>جستجو و فیلتر کاربران</t>
+  </si>
+  <si>
+    <t>غیرفعال‌سازی / حذف کاربر</t>
+  </si>
+  <si>
+    <t>قفل شدن حساب پس از چند بار ورود ناموفق</t>
+  </si>
+  <si>
+    <t>ثبت فعالیت‌های امنیتی (Login Logs / Audit Trail)</t>
+  </si>
+  <si>
+    <t>پروفایل کاربر (User Profile)</t>
+  </si>
+  <si>
+    <t>تأیید شماره موبایل (SMS Verification)</t>
+  </si>
+  <si>
+    <t>ورود دو مرحله‌ای (Two-Factor Authentication - 2FA)</t>
+  </si>
+  <si>
+    <t>تخصیص نقش‌ها و سطوح دسترسی (Access Control)</t>
+  </si>
+  <si>
+    <t>ویرایش اطلاعات کاربر توسط Admin</t>
+  </si>
+  <si>
+    <t>Session Management و خروج اجباری</t>
+  </si>
+  <si>
+    <t>تغییر وضعیت کاربران (Active / Inactive / Banned)</t>
   </si>
 </sst>
 </file>
@@ -343,14 +404,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -361,16 +416,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -387,11 +433,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="8">
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
     <dxf>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -415,10 +494,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table13" displayName="Table13" ref="C1:H49" totalsRowShown="0" headerRowDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table13" displayName="Table13" ref="C1:H49" totalsRowShown="0" headerRowDxfId="7">
   <autoFilter ref="C1:H49"/>
   <tableColumns count="6">
-    <tableColumn id="2" name="قابلیت/مورد" dataDxfId="1"/>
+    <tableColumn id="2" name="قابلیت/مورد" dataDxfId="6"/>
     <tableColumn id="3" name="توضیحات کوتاه"/>
     <tableColumn id="5" name="وضعیت"/>
     <tableColumn id="6" name="تاریخ شروع"/>
@@ -436,8 +515,20 @@
     <sortCondition ref="B1:B16"/>
   </sortState>
   <tableColumns count="2">
-    <tableColumn id="1" name="عنوان" dataDxfId="0"/>
+    <tableColumn id="1" name="عنوان" dataDxfId="5"/>
     <tableColumn id="2" name="اولویت"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:C21" totalsRowShown="0" headerRowDxfId="1" dataDxfId="2">
+  <autoFilter ref="A1:C21"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="ردیف" dataDxfId="4"/>
+    <tableColumn id="2" name="عنوان" dataDxfId="3"/>
+    <tableColumn id="3" name="وضعیت" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -718,645 +809,669 @@
     <col min="8" max="8" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+      <c r="A2" s="16">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="4" t="s">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="6" t="s">
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="10">
+      <c r="A5" s="12">
         <v>2</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="14" t="s">
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="14" t="s">
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="6" t="s">
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
+      <c r="A9" s="12">
         <v>3</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="11" t="s">
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="5" t="s">
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="10">
+      <c r="A12" s="12">
         <v>4</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="11" t="s">
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="6" t="s">
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="10">
+      <c r="A15" s="12">
         <v>5</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="14" t="s">
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="6" t="s">
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="10">
+      <c r="A18" s="12">
         <v>6</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="6" t="s">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="10">
+      <c r="A20" s="12">
         <v>7</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="5" t="s">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="10">
+      <c r="A22" s="12">
         <v>8</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="6" t="s">
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="10">
+      <c r="A24" s="12">
         <v>9</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="6" t="s">
+      <c r="A25" s="14"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="10">
+      <c r="A26" s="12">
         <v>10</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="14" t="s">
+      <c r="A27" s="13"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="6" t="s">
+      <c r="A28" s="14"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="10">
+      <c r="A29" s="12">
         <v>11</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="14" t="s">
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="6" t="s">
+      <c r="A31" s="14"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="10">
+      <c r="A32" s="12">
         <v>12</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="6" t="s">
+      <c r="A33" s="14"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="10">
+      <c r="A34" s="12">
         <v>13</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="6" t="s">
+      <c r="A35" s="14"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="10">
+      <c r="A36" s="12">
         <v>14</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B36" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="7"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="14" t="s">
+      <c r="A37" s="13"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="8"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="6" t="s">
+      <c r="A38" s="14"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="10">
+      <c r="A39" s="12">
         <v>15</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B39" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="7"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="14" t="s">
+      <c r="A40" s="13"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="11"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="14" t="s">
+      <c r="A41" s="13"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="7"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="14" t="s">
+      <c r="A42" s="13"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="11"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="7"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="14" t="s">
+      <c r="A43" s="13"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="7"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="14" t="s">
+      <c r="A44" s="13"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="8"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="6" t="s">
+      <c r="A45" s="14"/>
+      <c r="B45" s="14"/>
+      <c r="C45" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="10">
+      <c r="A46" s="12">
         <v>16</v>
       </c>
-      <c r="B46" s="10" t="s">
+      <c r="B46" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="2" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="4" t="s">
+      <c r="A47" s="15"/>
+      <c r="B47" s="15"/>
+      <c r="C47" s="2" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="4" t="s">
+      <c r="A48" s="15"/>
+      <c r="B48" s="15"/>
+      <c r="C48" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="4" t="s">
+      <c r="A49" s="15"/>
+      <c r="B49" s="15"/>
+      <c r="C49" s="2" t="s">
         <v>71</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:B49"/>
   <mergeCells count="32">
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="B26:B28"/>
     <mergeCell ref="B39:B45"/>
     <mergeCell ref="A39:A45"/>
     <mergeCell ref="B46:B49"/>
@@ -1365,30 +1480,6 @@
     <mergeCell ref="B34:B35"/>
     <mergeCell ref="B36:B38"/>
     <mergeCell ref="A36:A38"/>
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="B5:B8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -1402,11 +1493,11 @@
   <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.5703125" style="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="48.5703125" style="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="11" t="s">
         <v>73</v>
       </c>
       <c r="B1" t="s">
@@ -1414,7 +1505,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="10" t="s">
         <v>45</v>
       </c>
       <c r="B2">
@@ -1422,7 +1513,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="10" t="s">
         <v>25</v>
       </c>
       <c r="B3">
@@ -1430,7 +1521,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="10" t="s">
         <v>20</v>
       </c>
       <c r="B4">
@@ -1438,7 +1529,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="10" t="s">
         <v>16</v>
       </c>
       <c r="B5">
@@ -1446,7 +1537,7 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="10" t="s">
         <v>59</v>
       </c>
       <c r="B6">
@@ -1454,7 +1545,7 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="10" t="s">
         <v>49</v>
       </c>
       <c r="B7">
@@ -1462,7 +1553,7 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B8">
@@ -1470,7 +1561,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="10" t="s">
         <v>38</v>
       </c>
       <c r="B9">
@@ -1478,7 +1569,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="10" t="s">
         <v>29</v>
       </c>
       <c r="B10">
@@ -1486,7 +1577,7 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="10" t="s">
         <v>72</v>
       </c>
       <c r="B11">
@@ -1494,7 +1585,7 @@
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="10" t="s">
         <v>55</v>
       </c>
       <c r="B12">
@@ -1502,7 +1593,7 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="10" t="s">
         <v>41</v>
       </c>
       <c r="B13">
@@ -1510,7 +1601,7 @@
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="10" t="s">
         <v>52</v>
       </c>
       <c r="B14">
@@ -1518,13 +1609,202 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="10" t="s">
         <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="17"/>
+    <col min="2" max="2" width="44.5703125" style="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="17">
+        <v>1</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="17">
+        <v>2</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="17">
+        <v>3</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="17">
+        <v>4</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="17">
+        <v>5</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="17">
+        <v>6</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
+        <v>7</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
+        <v>8</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
+        <v>9</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>10</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
+        <v>11</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>12</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
+        <v>13</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
+        <v>14</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="17">
+        <v>15</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="17">
+        <v>17</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="17">
+        <v>18</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="17">
+        <v>19</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="17">
+        <v>20</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/فیچر لیست های زیرساخت.xlsx
+++ b/فیچر لیست های زیرساخت.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WFTProjects\WFTInfra\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WFTProject\WFTInfra\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6691033-5C38-444C-A61C-EC8001FC1FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7995" activeTab="2"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="لیست فیچرها" sheetId="2" r:id="rId1"/>
     <sheet name="اولویت بندی " sheetId="3" r:id="rId2"/>
     <sheet name="فیچر مدیریت کاربران" sheetId="4" r:id="rId3"/>
+    <sheet name="بدهی های فنی" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'اولویت بندی '!#REF!</definedName>
@@ -30,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="96">
   <si>
     <t>ردیف</t>
   </si>
@@ -315,12 +317,15 @@
   </si>
   <si>
     <t>تغییر وضعیت کاربران (Active / Inactive / Banned)</t>
+  </si>
+  <si>
+    <t>در AuthService باید به جای  استفاده مستقیم از UserDto  از دو موجودیت جدید به نام های UserLoginDto و RegisterLoginDto استفاده کرد</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -433,6 +438,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -442,14 +450,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" readingOrder="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -494,41 +499,52 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table13" displayName="Table13" ref="C1:H49" totalsRowShown="0" headerRowDxfId="7">
-  <autoFilter ref="C1:H49"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table13" displayName="Table13" ref="C1:H49" totalsRowShown="0" headerRowDxfId="7">
+  <autoFilter ref="C1:H49" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="6">
-    <tableColumn id="2" name="قابلیت/مورد" dataDxfId="6"/>
-    <tableColumn id="3" name="توضیحات کوتاه"/>
-    <tableColumn id="5" name="وضعیت"/>
-    <tableColumn id="6" name="تاریخ شروع"/>
-    <tableColumn id="7" name="تاریخ پایان"/>
-    <tableColumn id="8" name="توضیحات تکمیلی"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="قابلیت/مورد" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="توضیحات کوتاه"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="وضعیت"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="تاریخ شروع"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="تاریخ پایان"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="توضیحات تکمیلی"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:B16" totalsRowShown="0">
-  <autoFilter ref="A1:B16"/>
-  <sortState ref="A2:B16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table4" displayName="Table4" ref="A1:B16" totalsRowShown="0">
+  <autoFilter ref="A1:B16" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B16">
     <sortCondition ref="B1:B16"/>
   </sortState>
   <tableColumns count="2">
-    <tableColumn id="1" name="عنوان" dataDxfId="5"/>
-    <tableColumn id="2" name="اولویت"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="عنوان" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="اولویت"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:C21" totalsRowShown="0" headerRowDxfId="1" dataDxfId="2">
-  <autoFilter ref="A1:C21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:C21" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A1:C21" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="ردیف" dataDxfId="4"/>
-    <tableColumn id="2" name="عنوان" dataDxfId="3"/>
-    <tableColumn id="3" name="وضعیت" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="ردیف" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="عنوان" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="وضعیت" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9C38C941-0F05-4DC6-9DE9-26A9D8F8355D}" name="Table3" displayName="Table3" ref="A1:B2" totalsRowShown="0">
+  <autoFilter ref="A1:B2" xr:uid="{9C38C941-0F05-4DC6-9DE9-26A9D8F8355D}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{0A6FC9C8-096A-46FA-A9C1-FEDAD92C7FCF}" name="ردیف"/>
+    <tableColumn id="2" xr3:uid="{1A888F44-ECDD-4560-ABE3-9795A8B8F836}" name="عنوان"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -796,20 +812,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="48.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="61.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" customWidth="1"/>
-    <col min="8" max="8" width="15.85546875" customWidth="1"/>
+    <col min="2" max="2" width="48.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" customWidth="1"/>
+    <col min="8" max="8" width="15.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -835,7 +851,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="16">
         <v>1</v>
       </c>
@@ -846,16 +862,16 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
       <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
       <c r="C4" s="4" t="s">
         <v>11</v>
       </c>
@@ -865,11 +881,11 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="12">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="13">
         <v>2</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="13" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -881,9 +897,9 @@
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
       <c r="C6" s="9" t="s">
         <v>24</v>
       </c>
@@ -893,9 +909,9 @@
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
       <c r="C7" s="9" t="s">
         <v>14</v>
       </c>
@@ -905,9 +921,9 @@
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="15"/>
+      <c r="B8" s="15"/>
       <c r="C8" s="4" t="s">
         <v>15</v>
       </c>
@@ -917,11 +933,11 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="12">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="13">
         <v>3</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="13" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="6" t="s">
@@ -933,9 +949,9 @@
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13"/>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
       <c r="C10" s="6" t="s">
         <v>18</v>
       </c>
@@ -945,9 +961,9 @@
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="15"/>
+      <c r="B11" s="15"/>
       <c r="C11" s="3" t="s">
         <v>19</v>
       </c>
@@ -957,11 +973,11 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="12">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="13">
         <v>4</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="13" t="s">
         <v>20</v>
       </c>
       <c r="C12" s="7" t="s">
@@ -973,9 +989,9 @@
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
       <c r="C13" s="6" t="s">
         <v>22</v>
       </c>
@@ -985,9 +1001,9 @@
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="15"/>
+      <c r="B14" s="15"/>
       <c r="C14" s="4" t="s">
         <v>23</v>
       </c>
@@ -997,11 +1013,11 @@
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="12">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="13">
         <v>5</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C15" s="7" t="s">
@@ -1013,9 +1029,9 @@
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
-      <c r="B16" s="13"/>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
       <c r="C16" s="9" t="s">
         <v>27</v>
       </c>
@@ -1025,9 +1041,9 @@
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
       <c r="C17" s="4" t="s">
         <v>28</v>
       </c>
@@ -1037,11 +1053,11 @@
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="12">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="13">
         <v>6</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C18" s="8" t="s">
@@ -1053,9 +1069,9 @@
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
       <c r="C19" s="4" t="s">
         <v>31</v>
       </c>
@@ -1065,11 +1081,11 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="12">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="13">
         <v>7</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="13" t="s">
         <v>32</v>
       </c>
       <c r="C20" s="7" t="s">
@@ -1081,9 +1097,9 @@
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="15"/>
+      <c r="B21" s="15"/>
       <c r="C21" s="3" t="s">
         <v>34</v>
       </c>
@@ -1093,11 +1109,11 @@
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="12">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="13">
         <v>8</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="13" t="s">
         <v>35</v>
       </c>
       <c r="C22" s="8" t="s">
@@ -1109,9 +1125,9 @@
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="15"/>
+      <c r="B23" s="15"/>
       <c r="C23" s="4" t="s">
         <v>37</v>
       </c>
@@ -1121,11 +1137,11 @@
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="12">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="13">
         <v>9</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="13" t="s">
         <v>38</v>
       </c>
       <c r="C24" s="8" t="s">
@@ -1137,9 +1153,9 @@
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="14"/>
-      <c r="B25" s="14"/>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="15"/>
+      <c r="B25" s="15"/>
       <c r="C25" s="4" t="s">
         <v>40</v>
       </c>
@@ -1149,11 +1165,11 @@
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="12">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="13">
         <v>10</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="13" t="s">
         <v>41</v>
       </c>
       <c r="C26" s="8" t="s">
@@ -1165,9 +1181,9 @@
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="13"/>
-      <c r="B27" s="13"/>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="14"/>
+      <c r="B27" s="14"/>
       <c r="C27" s="9" t="s">
         <v>43</v>
       </c>
@@ -1177,9 +1193,9 @@
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="14"/>
-      <c r="B28" s="14"/>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
       <c r="C28" s="4" t="s">
         <v>44</v>
       </c>
@@ -1189,11 +1205,11 @@
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="12">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="13">
         <v>11</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="13" t="s">
         <v>45</v>
       </c>
       <c r="C29" s="8" t="s">
@@ -1205,9 +1221,9 @@
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="14"/>
+      <c r="B30" s="14"/>
       <c r="C30" s="9" t="s">
         <v>47</v>
       </c>
@@ -1217,9 +1233,9 @@
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="14"/>
-      <c r="B31" s="14"/>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="15"/>
+      <c r="B31" s="15"/>
       <c r="C31" s="4" t="s">
         <v>48</v>
       </c>
@@ -1229,11 +1245,11 @@
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="12">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="13">
         <v>12</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="13" t="s">
         <v>49</v>
       </c>
       <c r="C32" s="8" t="s">
@@ -1245,9 +1261,9 @@
       <c r="G32" s="7"/>
       <c r="H32" s="7"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="14"/>
-      <c r="B33" s="14"/>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="15"/>
+      <c r="B33" s="15"/>
       <c r="C33" s="4" t="s">
         <v>51</v>
       </c>
@@ -1257,11 +1273,11 @@
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="12">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="13">
         <v>13</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="13" t="s">
         <v>52</v>
       </c>
       <c r="C34" s="8" t="s">
@@ -1273,9 +1289,9 @@
       <c r="G34" s="7"/>
       <c r="H34" s="7"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="14"/>
-      <c r="B35" s="14"/>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="15"/>
+      <c r="B35" s="15"/>
       <c r="C35" s="4" t="s">
         <v>54</v>
       </c>
@@ -1285,11 +1301,11 @@
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="12">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="13">
         <v>14</v>
       </c>
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="13" t="s">
         <v>55</v>
       </c>
       <c r="C36" s="8" t="s">
@@ -1301,9 +1317,9 @@
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="13"/>
-      <c r="B37" s="13"/>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="14"/>
+      <c r="B37" s="14"/>
       <c r="C37" s="9" t="s">
         <v>57</v>
       </c>
@@ -1313,9 +1329,9 @@
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="14"/>
-      <c r="B38" s="14"/>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="15"/>
+      <c r="B38" s="15"/>
       <c r="C38" s="4" t="s">
         <v>58</v>
       </c>
@@ -1325,11 +1341,11 @@
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="12">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="13">
         <v>15</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="B39" s="13" t="s">
         <v>59</v>
       </c>
       <c r="C39" s="8" t="s">
@@ -1341,9 +1357,9 @@
       <c r="G39" s="7"/>
       <c r="H39" s="7"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="13"/>
-      <c r="B40" s="13"/>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="14"/>
+      <c r="B40" s="14"/>
       <c r="C40" s="9" t="s">
         <v>61</v>
       </c>
@@ -1353,9 +1369,9 @@
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="13"/>
-      <c r="B41" s="13"/>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="14"/>
+      <c r="B41" s="14"/>
       <c r="C41" s="9" t="s">
         <v>62</v>
       </c>
@@ -1365,9 +1381,9 @@
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="13"/>
-      <c r="B42" s="13"/>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="14"/>
+      <c r="B42" s="14"/>
       <c r="C42" s="9" t="s">
         <v>63</v>
       </c>
@@ -1377,9 +1393,9 @@
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="13"/>
-      <c r="B43" s="13"/>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="14"/>
+      <c r="B43" s="14"/>
       <c r="C43" s="9" t="s">
         <v>64</v>
       </c>
@@ -1389,9 +1405,9 @@
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="13"/>
-      <c r="B44" s="13"/>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="14"/>
+      <c r="B44" s="14"/>
       <c r="C44" s="9" t="s">
         <v>65</v>
       </c>
@@ -1401,9 +1417,9 @@
       <c r="G44" s="6"/>
       <c r="H44" s="6"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="14"/>
-      <c r="B45" s="14"/>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="15"/>
+      <c r="B45" s="15"/>
       <c r="C45" s="4" t="s">
         <v>66</v>
       </c>
@@ -1413,41 +1429,65 @@
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="12">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" s="13">
         <v>16</v>
       </c>
-      <c r="B46" s="12" t="s">
+      <c r="B46" s="13" t="s">
         <v>67</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="15"/>
-      <c r="B47" s="15"/>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" s="17"/>
+      <c r="B47" s="17"/>
       <c r="C47" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="15"/>
-      <c r="B48" s="15"/>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="17"/>
+      <c r="B48" s="17"/>
       <c r="C48" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="15"/>
-      <c r="B49" s="15"/>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="17"/>
+      <c r="B49" s="17"/>
       <c r="C49" s="2" t="s">
         <v>71</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B49"/>
+  <autoFilter ref="A1:B49" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="32">
+    <mergeCell ref="B39:B45"/>
+    <mergeCell ref="A39:A45"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="A12:A14"/>
@@ -1456,30 +1496,6 @@
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="A5:A8"/>
     <mergeCell ref="B5:B8"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="B39:B45"/>
-    <mergeCell ref="A39:A45"/>
-    <mergeCell ref="B46:B49"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="A36:A38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -1489,14 +1505,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="48.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="48.5546875" style="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>73</v>
       </c>
@@ -1504,7 +1520,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>45</v>
       </c>
@@ -1512,7 +1528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>25</v>
       </c>
@@ -1520,7 +1536,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>20</v>
       </c>
@@ -1528,7 +1544,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>16</v>
       </c>
@@ -1536,7 +1552,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>59</v>
       </c>
@@ -1544,7 +1560,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>49</v>
       </c>
@@ -1552,7 +1568,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>35</v>
       </c>
@@ -1560,7 +1576,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>38</v>
       </c>
@@ -1568,7 +1584,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>29</v>
       </c>
@@ -1576,7 +1592,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>72</v>
       </c>
@@ -1584,7 +1600,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
         <v>55</v>
       </c>
@@ -1592,7 +1608,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
         <v>41</v>
       </c>
@@ -1600,7 +1616,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
         <v>52</v>
       </c>
@@ -1608,12 +1624,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
         <v>32</v>
       </c>
@@ -1627,184 +1643,216 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="17"/>
-    <col min="2" max="2" width="44.5703125" style="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="17"/>
+    <col min="1" max="1" width="9.109375" style="12"/>
+    <col min="2" max="2" width="44.5546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.109375" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="12" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="17">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="12">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="12" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="17">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="12">
         <v>2</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="12" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="17">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="12" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="17">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="12">
         <v>4</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="12" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="17">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="12">
         <v>5</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="12" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="17">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="12">
         <v>6</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="12" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="17">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="12">
         <v>7</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="12" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="17">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="12">
         <v>8</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="12" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="17">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="12">
         <v>9</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="12" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="17">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="12">
         <v>10</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="12" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="17">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="12">
         <v>11</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="12" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="17">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="12">
         <v>12</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="12" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="17">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="12">
         <v>13</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="17">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="12">
         <v>14</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="12" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="17">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="12">
         <v>15</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="12" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="17">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="12">
         <v>16</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="12" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="17">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="12">
         <v>17</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="12" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="17">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="12">
         <v>18</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="12" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="17">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="12">
         <v>19</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="12" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="17">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="12">
         <v>20</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="12" t="s">
         <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B02AC3A3-43A0-47B5-82EF-96E8596EF615}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="100.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/فیچر لیست های زیرساخت.xlsx
+++ b/فیچر لیست های زیرساخت.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WFTProject\WFTInfra\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WFTProjects\WFTInfra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6691033-5C38-444C-A61C-EC8001FC1FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
   </bookViews>
   <sheets>
     <sheet name="لیست فیچرها" sheetId="2" r:id="rId1"/>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="95">
   <si>
     <t>ردیف</t>
   </si>
@@ -56,9 +55,6 @@
   </si>
   <si>
     <t>دسته بندی</t>
-  </si>
-  <si>
-    <t>مدیریت پیکربندی (Configuration</t>
   </si>
   <si>
     <t>بارگذاری تنظیمات از فایل (مثل appsettings.json)</t>
@@ -325,7 +321,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -450,10 +446,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -499,52 +495,52 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table13" displayName="Table13" ref="C1:H49" totalsRowShown="0" headerRowDxfId="7">
-  <autoFilter ref="C1:H49" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table13" displayName="Table13" ref="C1:H49" totalsRowShown="0" headerRowDxfId="7">
+  <autoFilter ref="C1:H49"/>
   <tableColumns count="6">
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="قابلیت/مورد" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="توضیحات کوتاه"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="وضعیت"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="تاریخ شروع"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="تاریخ پایان"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="توضیحات تکمیلی"/>
+    <tableColumn id="2" name="قابلیت/مورد" dataDxfId="6"/>
+    <tableColumn id="3" name="توضیحات کوتاه"/>
+    <tableColumn id="5" name="وضعیت"/>
+    <tableColumn id="6" name="تاریخ شروع"/>
+    <tableColumn id="7" name="تاریخ پایان"/>
+    <tableColumn id="8" name="توضیحات تکمیلی"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table4" displayName="Table4" ref="A1:B16" totalsRowShown="0">
-  <autoFilter ref="A1:B16" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:B16" totalsRowShown="0">
+  <autoFilter ref="A1:B16"/>
+  <sortState ref="A2:B16">
     <sortCondition ref="B1:B16"/>
   </sortState>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="عنوان" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="اولویت"/>
+    <tableColumn id="1" name="عنوان" dataDxfId="5"/>
+    <tableColumn id="2" name="اولویت"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:C21" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="A1:C21" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:C21" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A1:C21"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="ردیف" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="عنوان" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="وضعیت" dataDxfId="0"/>
+    <tableColumn id="1" name="ردیف" dataDxfId="2"/>
+    <tableColumn id="2" name="عنوان" dataDxfId="1"/>
+    <tableColumn id="3" name="وضعیت" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9C38C941-0F05-4DC6-9DE9-26A9D8F8355D}" name="Table3" displayName="Table3" ref="A1:B2" totalsRowShown="0">
-  <autoFilter ref="A1:B2" xr:uid="{9C38C941-0F05-4DC6-9DE9-26A9D8F8355D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:B2" totalsRowShown="0">
+  <autoFilter ref="A1:B2"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{0A6FC9C8-096A-46FA-A9C1-FEDAD92C7FCF}" name="ردیف"/>
-    <tableColumn id="2" xr3:uid="{1A888F44-ECDD-4560-ABE3-9795A8B8F836}" name="عنوان"/>
+    <tableColumn id="1" name="ردیف"/>
+    <tableColumn id="2" name="عنوان"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -812,20 +808,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="48.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="61.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" customWidth="1"/>
-    <col min="6" max="6" width="11.6640625" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" customWidth="1"/>
-    <col min="8" max="8" width="15.88671875" customWidth="1"/>
+    <col min="2" max="2" width="48.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -851,29 +847,29 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="16">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="17">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="14"/>
       <c r="B3" s="14"/>
       <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="15"/>
       <c r="B4" s="15"/>
       <c r="C4" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -881,15 +877,15 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
         <v>2</v>
       </c>
       <c r="B5" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>13</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
@@ -897,11 +893,11 @@
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="14"/>
       <c r="B6" s="14"/>
       <c r="C6" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
@@ -909,11 +905,11 @@
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="14"/>
       <c r="C7" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
@@ -921,11 +917,11 @@
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -933,15 +929,15 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="13">
         <v>3</v>
       </c>
       <c r="B9" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>16</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
@@ -949,11 +945,11 @@
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="14"/>
       <c r="B10" s="14"/>
       <c r="C10" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
@@ -961,11 +957,11 @@
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="15"/>
       <c r="B11" s="15"/>
       <c r="C11" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -973,15 +969,15 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="13">
         <v>4</v>
       </c>
       <c r="B12" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>20</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>21</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
@@ -989,11 +985,11 @@
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="14"/>
       <c r="B13" s="14"/>
       <c r="C13" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
@@ -1001,11 +997,11 @@
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="15"/>
       <c r="B14" s="15"/>
       <c r="C14" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -1013,15 +1009,15 @@
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="13">
         <v>5</v>
       </c>
       <c r="B15" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>25</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>26</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
@@ -1029,11 +1025,11 @@
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="14"/>
       <c r="B16" s="14"/>
       <c r="C16" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
@@ -1041,11 +1037,11 @@
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="15"/>
       <c r="B17" s="15"/>
       <c r="C17" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -1053,15 +1049,15 @@
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="13">
         <v>6</v>
       </c>
       <c r="B18" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>29</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>30</v>
       </c>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
@@ -1069,11 +1065,11 @@
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="15"/>
       <c r="B19" s="15"/>
       <c r="C19" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -1081,43 +1077,47 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="13">
         <v>7</v>
       </c>
       <c r="B20" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>33</v>
-      </c>
       <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
+      <c r="E20" s="7">
+        <v>1</v>
+      </c>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="15"/>
       <c r="B21" s="15"/>
       <c r="C21" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
+      <c r="E21" s="3">
+        <v>1</v>
+      </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="13">
         <v>8</v>
       </c>
       <c r="B22" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>36</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
@@ -1125,11 +1125,11 @@
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="15"/>
       <c r="B23" s="15"/>
       <c r="C23" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
@@ -1137,15 +1137,15 @@
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="13">
         <v>9</v>
       </c>
       <c r="B24" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>39</v>
       </c>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
@@ -1153,11 +1153,11 @@
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="15"/>
       <c r="B25" s="15"/>
       <c r="C25" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
@@ -1165,15 +1165,15 @@
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="13">
         <v>10</v>
       </c>
       <c r="B26" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>41</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>42</v>
       </c>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
@@ -1181,11 +1181,11 @@
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="14"/>
       <c r="B27" s="14"/>
       <c r="C27" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -1193,11 +1193,11 @@
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="15"/>
       <c r="C28" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
@@ -1205,27 +1205,29 @@
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="13">
         <v>11</v>
       </c>
       <c r="B29" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="8" t="s">
-        <v>46</v>
-      </c>
       <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
+      <c r="E29" s="7">
+        <v>1</v>
+      </c>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="14"/>
       <c r="B30" s="14"/>
       <c r="C30" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
@@ -1233,11 +1235,11 @@
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="15"/>
       <c r="B31" s="15"/>
       <c r="C31" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
@@ -1245,15 +1247,15 @@
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="13">
         <v>12</v>
       </c>
       <c r="B32" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" s="8" t="s">
         <v>49</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>50</v>
       </c>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
@@ -1261,11 +1263,11 @@
       <c r="G32" s="7"/>
       <c r="H32" s="7"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="15"/>
       <c r="B33" s="15"/>
       <c r="C33" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
@@ -1273,27 +1275,29 @@
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="13">
         <v>13</v>
       </c>
       <c r="B34" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="8" t="s">
-        <v>53</v>
-      </c>
       <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
+      <c r="E34" s="7">
+        <v>1</v>
+      </c>
       <c r="F34" s="7"/>
       <c r="G34" s="7"/>
       <c r="H34" s="7"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="15"/>
       <c r="B35" s="15"/>
       <c r="C35" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
@@ -1301,15 +1305,15 @@
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="13">
         <v>14</v>
       </c>
       <c r="B36" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>55</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>56</v>
       </c>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
@@ -1317,11 +1321,11 @@
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="14"/>
       <c r="B37" s="14"/>
       <c r="C37" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
@@ -1329,11 +1333,11 @@
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="15"/>
       <c r="B38" s="15"/>
       <c r="C38" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
@@ -1341,15 +1345,15 @@
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="13">
         <v>15</v>
       </c>
       <c r="B39" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C39" s="8" t="s">
         <v>59</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>60</v>
       </c>
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
@@ -1357,11 +1361,11 @@
       <c r="G39" s="7"/>
       <c r="H39" s="7"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="14"/>
       <c r="B40" s="14"/>
       <c r="C40" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
@@ -1369,11 +1373,11 @@
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="14"/>
       <c r="B41" s="14"/>
       <c r="C41" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
@@ -1381,11 +1385,11 @@
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="14"/>
       <c r="B42" s="14"/>
       <c r="C42" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
@@ -1393,11 +1397,11 @@
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="14"/>
       <c r="B43" s="14"/>
       <c r="C43" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
@@ -1405,11 +1409,11 @@
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="14"/>
       <c r="B44" s="14"/>
       <c r="C44" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
@@ -1417,11 +1421,11 @@
       <c r="G44" s="6"/>
       <c r="H44" s="6"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="15"/>
       <c r="B45" s="15"/>
       <c r="C45" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -1429,41 +1433,65 @@
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="13">
         <v>16</v>
       </c>
       <c r="B46" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C46" s="2" t="s">
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="16"/>
+      <c r="B47" s="16"/>
+      <c r="C47" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="17"/>
-      <c r="B47" s="17"/>
-      <c r="C47" s="2" t="s">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="16"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="17"/>
-      <c r="B48" s="17"/>
-      <c r="C48" s="2" t="s">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="16"/>
+      <c r="B49" s="16"/>
+      <c r="C49" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="17"/>
-      <c r="B49" s="17"/>
-      <c r="C49" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:B49" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:B49"/>
   <mergeCells count="32">
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="B26:B28"/>
     <mergeCell ref="B39:B45"/>
     <mergeCell ref="A39:A45"/>
     <mergeCell ref="B46:B49"/>
@@ -1472,30 +1500,6 @@
     <mergeCell ref="B34:B35"/>
     <mergeCell ref="B36:B38"/>
     <mergeCell ref="A36:A38"/>
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="B5:B8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -1505,133 +1509,133 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="48.5703125" style="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" t="s">
         <v>73</v>
       </c>
-      <c r="B1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B14">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1643,184 +1647,193 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="12"/>
-    <col min="2" max="2" width="44.5546875" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.109375" style="12"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="44.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C1" s="12" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="12">
         <v>1</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+      <c r="C2" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="12">
         <v>2</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+      <c r="C3" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="12">
         <v>3</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>4</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="C5" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>5</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>6</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>7</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>8</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
         <v>9</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="12">
         <v>10</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="12">
         <v>11</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="12">
         <v>12</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="12">
         <v>13</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="12">
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="12">
         <v>15</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="12">
         <v>16</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="12">
         <v>17</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="12">
         <v>18</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="12">
         <v>19</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="12">
         <v>20</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1832,27 +1845,27 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B02AC3A3-43A0-47B5-82EF-96E8596EF615}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="100.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="100.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
